--- a/artfynd/A 6158-2026 artfynd.xlsx
+++ b/artfynd/A 6158-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448228</v>
       </c>
       <c r="B2" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>131448225</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131448222</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131448224</v>
       </c>
       <c r="B7" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6158-2026 artfynd.xlsx
+++ b/artfynd/A 6158-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448228</v>
       </c>
       <c r="B2" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131448221</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448223</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>131448225</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131448222</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131448224</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6158-2026 artfynd.xlsx
+++ b/artfynd/A 6158-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448228</v>
       </c>
       <c r="B2" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131448221</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448223</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>131448225</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131448222</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>131448224</v>
       </c>
       <c r="B7" t="n">
-        <v>79277</v>
+        <v>79278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 6158-2026 artfynd.xlsx
+++ b/artfynd/A 6158-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131448228</v>
+        <v>131448220</v>
       </c>
       <c r="B2" t="n">
-        <v>78940</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386322</v>
+        <v>386217</v>
       </c>
       <c r="R2" t="n">
-        <v>6758001</v>
+        <v>6758038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448223</v>
+        <v>131448228</v>
       </c>
       <c r="B3" t="n">
-        <v>57100</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386311</v>
+        <v>386322</v>
       </c>
       <c r="R3" t="n">
-        <v>6758002</v>
+        <v>6758001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448221</v>
+        <v>131448218</v>
       </c>
       <c r="B4" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386272</v>
+        <v>386148</v>
       </c>
       <c r="R4" t="n">
-        <v>6757983</v>
+        <v>6758017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448225</v>
+        <v>131448219</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386285</v>
+        <v>386230</v>
       </c>
       <c r="R5" t="n">
-        <v>6758011</v>
+        <v>6758036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,11 +1106,11 @@
         <v>131448222</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1220,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131448224</v>
+        <v>131448225</v>
       </c>
       <c r="B7" t="n">
-        <v>79298</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386301</v>
+        <v>386285</v>
       </c>
       <c r="R7" t="n">
-        <v>6758006</v>
+        <v>6758011</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,6 +1314,658 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131448226</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>386338</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6757999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131448227</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>386336</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6758002</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131448224</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>386301</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6758006</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131448229</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>386342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6758000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131448221</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>386272</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6757983</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131448223</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>386311</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6758002</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6158-2026 artfynd.xlsx
+++ b/artfynd/A 6158-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448220</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448218</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448219</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448222</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448226</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448227</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448224</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448229</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448221</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,8 +2026,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448223</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>